--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_252_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_252_R26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1045</v>
+        <v>3.416</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2033</v>
+        <v>3.5795</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0988</v>
+        <v>-0.1635</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6609</v>
+        <v>1.576</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0527</v>
+        <v>0.2042</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3918</v>
+        <v>1.3718</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6119</v>
+        <v>2.4195</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9494</v>
+        <v>0.1008</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6625</v>
+        <v>2.3187</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9509</v>
+        <v>-0.8435</v>
       </c>
       <c r="N2" t="n">
         <v>0.1034</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0543</v>
+        <v>-0.9469</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8352</v>
+        <v>1.1442</v>
       </c>
       <c r="T2" t="n">
-        <v>1.679</v>
+        <v>1.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1562</v>
+        <v>-0.0158</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7336</v>
+        <v>3.1622</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2183</v>
+        <v>3.7315</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5153</v>
+        <v>-0.5693</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3589</v>
+        <v>0.6609</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4826</v>
+        <v>2.0527</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1237</v>
+        <v>-1.3918</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1629</v>
+        <v>2.6119</v>
       </c>
       <c r="K3" t="n">
-        <v>0.39</v>
+        <v>1.9494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7729</v>
+        <v>0.6625</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.804</v>
+        <v>-1.9509</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0926</v>
+        <v>0.1034</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8966</v>
+        <v>-2.0543</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4469</v>
+        <v>1.8929</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2151</v>
+        <v>1.2072</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2318</v>
+        <v>0.6858</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6355</v>
+        <v>2.8749</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9334</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2979</v>
+        <v>2.2465</v>
       </c>
       <c r="G4" t="n">
-        <v>1.576</v>
+        <v>0.3589</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2042</v>
+        <v>0.4826</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3718</v>
+        <v>-0.1237</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4195</v>
+        <v>1.1629</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1008</v>
+        <v>0.39</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3187</v>
+        <v>0.7729</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8435</v>
+        <v>-0.804</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1034</v>
+        <v>0.0926</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9469</v>
+        <v>-0.8966</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3636</v>
+        <v>1.5883</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5138</v>
+        <v>0.6253</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1502</v>
+        <v>0.963</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2215</v>
+        <v>2.6703</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0677</v>
+        <v>3.1319</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2892</v>
+        <v>-0.4616</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.6391</v>
+        <v>1.0355</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5679</v>
+        <v>1.8955</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0711</v>
+        <v>-0.86</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.7143</v>
+        <v>4.3553</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.4361</v>
+        <v>2.0033</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2783</v>
+        <v>2.352</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07530000000000001</v>
+        <v>-3.3198</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8681</v>
+        <v>-0.1078</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7929</v>
+        <v>-3.212</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>4.791</v>
+        <v>1.8615</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6646</v>
+        <v>1.1837</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1264</v>
+        <v>0.6778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>1.8608</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5415</v>
+        <v>1.4622</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0703</v>
+        <v>-1.1887</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5288</v>
+        <v>2.6509</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0355</v>
+        <v>1.4057</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8955</v>
+        <v>1.1113</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.86</v>
+        <v>0.2943</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3553</v>
+        <v>2.306</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0033</v>
+        <v>0.8507</v>
       </c>
       <c r="L6" t="n">
-        <v>2.352</v>
+        <v>1.4552</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3198</v>
+        <v>-0.9003</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1078</v>
+        <v>0.2606</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.212</v>
+        <v>-1.1609</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0876</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>-4.639</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7328</v>
+        <v>2.0513</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1221</v>
+        <v>1.1444</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6106</v>
+        <v>0.9069</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8608</v>
+        <v>0.7886</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0.7886</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1255</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4246</v>
+        <v>1.1315</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5501</v>
+        <v>-0.6129</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4057</v>
+        <v>0.1379</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1113</v>
+        <v>1.3022</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2943</v>
+        <v>-1.1643</v>
       </c>
       <c r="J7" t="n">
-        <v>2.306</v>
+        <v>2.6178</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8507</v>
+        <v>0.9382</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4552</v>
+        <v>1.6796</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9003</v>
+        <v>-2.4799</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2606</v>
+        <v>0.364</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1609</v>
+        <v>-2.8439</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7834</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.639</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7146</v>
+        <v>1.1125</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9085</v>
+        <v>0.6372</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8061</v>
+        <v>0.4753</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7886</v>
+        <v>1.3558</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3402</v>
+        <v>0.503</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.542</v>
+        <v>-2.719</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2018</v>
+        <v>3.222</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3698</v>
+        <v>-3.6391</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4706</v>
+        <v>-1.5679</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8404</v>
+        <v>-2.0711</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8595</v>
+        <v>-3.7143</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8739</v>
+        <v>-2.4361</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7334</v>
+        <v>-1.2783</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4897</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5967</v>
+        <v>0.8681</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.107</v>
+        <v>-0.7929</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0606</v>
+        <v>3.0725</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5228</v>
+        <v>2.0133</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4621</v>
+        <v>1.0592</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4643</v>
+        <v>0.1823</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7205</v>
+        <v>-1.9523</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1849</v>
+        <v>2.1346</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.062</v>
+        <v>-0.3698</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1224</v>
+        <v>1.4706</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1844</v>
+        <v>-1.8404</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3744</v>
+        <v>-0.8595</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1275</v>
+        <v>0.8739</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5018</v>
+        <v>-1.7334</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4364</v>
+        <v>0.4897</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2499</v>
+        <v>0.5967</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6862</v>
+        <v>-0.107</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.188</v>
+        <v>0.4619</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>0.067</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1581</v>
+        <v>0.3949</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6773</v>
+        <v>0.0062</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.7205</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7473</v>
+        <v>-0.7144</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1379</v>
+        <v>-1.062</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3022</v>
+        <v>0.1224</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1643</v>
+        <v>-1.1844</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6178</v>
+        <v>0.3744</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9382</v>
+        <v>-0.1275</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6796</v>
+        <v>0.5018</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4799</v>
+        <v>-1.4364</v>
       </c>
       <c r="N10" t="n">
-        <v>0.364</v>
+        <v>0.2499</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8439</v>
+        <v>-1.6862</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0835</v>
+        <v>0.6585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4244</v>
+        <v>0.3462</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3409</v>
+        <v>0.3123</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3558</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.787</v>
+        <v>-3.7027</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4405</v>
+        <v>-1.3226</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3465</v>
+        <v>-2.3801</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0482</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4415</v>
+        <v>0.5258</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5034</v>
+        <v>0.6214</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0619</v>
+        <v>-0.0955</v>
       </c>
       <c r="V11" t="n">
         <v>0.2836</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0933</v>
+        <v>11.093</v>
       </c>
       <c r="E12" t="n">
-        <v>5.740999999999999</v>
+        <v>5.740800000000002</v>
       </c>
       <c r="F12" t="n">
         <v>5.3522</v>
@@ -1366,7 +1366,7 @@
         <v>10.2062</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8124</v>
+        <v>2.812399999999999</v>
       </c>
       <c r="L12" t="n">
         <v>7.3935</v>
@@ -1390,13 +1390,13 @@
         <v>13.9173</v>
       </c>
       <c r="S12" t="n">
-        <v>14.3695</v>
+        <v>14.3694</v>
       </c>
       <c r="T12" t="n">
-        <v>9.005499999999998</v>
+        <v>9.005699999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>5.363900000000001</v>
+        <v>5.3639</v>
       </c>
       <c r="V12" t="n">
         <v>4.147</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6744</v>
+        <v>1.4757</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4469</v>
+        <v>0.8793</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7725</v>
+        <v>0.5964</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0504</v>
+        <v>0.6279</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2172</v>
+        <v>0.4036</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.2242</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1802</v>
+        <v>2.6475</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8184</v>
+        <v>0.9446</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3618</v>
+        <v>1.703</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1298</v>
+        <v>-2.0197</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6012</v>
+        <v>-0.5409</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5286</v>
+        <v>-1.4787</v>
       </c>
       <c r="P13" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>3.2473</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1415</v>
+        <v>-1.9175</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2151</v>
+        <v>-0.892</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3566</v>
+        <v>-1.0255</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4665</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7886</v>
+        <v>0.2836</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1447</v>
+        <v>1.0478</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5255</v>
+        <v>-0.0726</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3808</v>
+        <v>1.1204</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6279</v>
+        <v>2.2861</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4036</v>
+        <v>-2.4082</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2242</v>
+        <v>4.6943</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6475</v>
+        <v>3.1154</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9446</v>
+        <v>-2.268</v>
       </c>
       <c r="L14" t="n">
-        <v>1.703</v>
+        <v>5.3834</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0197</v>
+        <v>-0.8293</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5409</v>
+        <v>-0.1401</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4787</v>
+        <v>-0.6891</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2473</v>
+        <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2486</v>
+        <v>-1.4703</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2459</v>
+        <v>-0.8685</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.0028</v>
+        <v>-0.6018</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0484</v>
+        <v>0.3206</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3085</v>
+        <v>1.6213</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3569</v>
+        <v>-1.3007</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2861</v>
+        <v>2.0504</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.4082</v>
+        <v>1.2172</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6943</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1154</v>
+        <v>3.1802</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.268</v>
+        <v>1.8184</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3834</v>
+        <v>1.3618</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8293</v>
+        <v>-1.1298</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1401</v>
+        <v>-0.6012</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6891</v>
+        <v>-0.5286</v>
       </c>
       <c r="P15" t="n">
         <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4697</v>
+        <v>-0.4953</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1044</v>
+        <v>0.3894</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3653</v>
+        <v>-0.8847</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5624</v>
+        <v>-0.1249</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3375</v>
+        <v>1.6863</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7751</v>
+        <v>-1.8112</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.147</v>
+        <v>1.763</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2508</v>
+        <v>-1.0308</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1038</v>
+        <v>2.7938</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5715</v>
+        <v>2.9715</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1646</v>
+        <v>-0.6687</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7361</v>
+        <v>3.6402</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7186</v>
+        <v>-1.2085</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0862</v>
+        <v>-0.3621</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6323</v>
+        <v>-0.8464</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-1.831</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-1.2852</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.5458</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6468</v>
+        <v>-2.1444</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6468</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3545</v>
+        <v>-0.2707</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5683</v>
+        <v>-2.3375</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9228</v>
+        <v>2.0668</v>
       </c>
       <c r="G17" t="n">
-        <v>1.763</v>
+        <v>-0.147</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0308</v>
+        <v>-0.2508</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7938</v>
+        <v>0.1038</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9715</v>
+        <v>0.5715</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6687</v>
+        <v>-0.1646</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6402</v>
+        <v>0.7361</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2085</v>
+        <v>-0.7186</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3621</v>
+        <v>-0.0862</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8464</v>
+        <v>-0.6323</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.0606</v>
+        <v>-0.3066</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4031</v>
+        <v>-0.5895</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.6575</v>
+        <v>0.2829</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1444</v>
+        <v>0.6468</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3818</v>
+        <v>-0.5226</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2586</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1232</v>
+        <v>-0.6178</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3939</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9158</v>
+        <v>-1.0565</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1769</v>
+        <v>-0.6715</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5117</v>
+        <v>-1.3481</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9453</v>
+        <v>-0.8274</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5664</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2237</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.4285</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2188</v>
+        <v>-0.1731</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6411</v>
+        <v>-1.871</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6639</v>
+        <v>-2.5495</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3051</v>
+        <v>0.6784</v>
       </c>
       <c r="G20" t="n">
-        <v>0.43</v>
+        <v>0.2539</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8415</v>
+        <v>-0.0707</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4115</v>
+        <v>0.3246</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6344</v>
+        <v>0.5757</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0958</v>
+        <v>0.0371</v>
       </c>
       <c r="L20" t="n">
         <v>0.5386</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2044</v>
+        <v>-0.3219</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2543</v>
+        <v>-0.1078</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.214</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3005</v>
+        <v>-1.1971</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0474</v>
+        <v>-0.8057</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3479</v>
+        <v>-0.3914</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0026</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3872</v>
+        <v>-2.0837</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5495</v>
+        <v>0.3101</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1623</v>
+        <v>-2.3938</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2539</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0707</v>
+        <v>0.8415</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3246</v>
+        <v>-0.4115</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5757</v>
+        <v>1.6344</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0371</v>
+        <v>1.0958</v>
       </c>
       <c r="L21" t="n">
         <v>0.5386</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3219</v>
+        <v>-1.2044</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1078</v>
+        <v>-0.2543</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.214</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7133</v>
+        <v>-0.7431</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8057</v>
+        <v>-0.3064</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9076</v>
+        <v>-0.4367</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1218</v>
+        <v>-2.9981</v>
       </c>
       <c r="E22" t="n">
         <v>-4.1574</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0357</v>
+        <v>1.1593</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7026</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.329</v>
+        <v>-0.2054</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3655</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0365</v>
+        <v>0.1601</v>
       </c>
       <c r="V22" t="n">
         <v>0.1418</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.093</v>
+        <v>-6.374999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3522</v>
+        <v>-5.352199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.7408</v>
+        <v>-1.0229</v>
       </c>
       <c r="G23" t="n">
         <v>3.944099999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.257199999999999</v>
+        <v>-5.2572</v>
       </c>
       <c r="I23" t="n">
         <v>9.2013</v>
@@ -2224,7 +2224,7 @@
         <v>14.1502</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4446</v>
+        <v>-2.444599999999999</v>
       </c>
       <c r="L23" t="n">
         <v>16.5949</v>
@@ -2233,13 +2233,13 @@
         <v>-10.2063</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.812400000000001</v>
+        <v>-2.8124</v>
       </c>
       <c r="O23" t="n">
         <v>-7.3935</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4794</v>
+        <v>3.479400000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.9173</v>
@@ -2248,13 +2248,13 @@
         <v>17.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>-14.3695</v>
+        <v>-9.651299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.3639</v>
+        <v>-5.364</v>
       </c>
       <c r="U23" t="n">
-        <v>-9.005699999999999</v>
+        <v>-4.2875</v>
       </c>
       <c r="V23" t="n">
         <v>-4.147</v>
